--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2955" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2994" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -814,6 +814,9 @@
   </si>
   <si>
     <t>Condition.category</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>problem-list-item | encounter-diagnosis</t>
@@ -855,6 +858,27 @@
     &lt;system value="http://snomed.info/sct"/&gt;
     &lt;code value="394593009"/&gt;
     &lt;display value="Medical oncology (qualifier value)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Condition.category:onkologie</t>
+  </si>
+  <si>
+    <t>onkologie</t>
+  </si>
+  <si>
+    <t>Onkologie-Kennzeichnung</t>
+  </si>
+  <si>
+    <t>Kennzeichnet die Diagnose als onkologische Diagnose des KDS-Moduls Onkologie und macht sie über die category-Suche auffindbar</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="55342001"/&gt;
+    &lt;display value="Neoplastic disease"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1858,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.828125" customWidth="true" bestFit="true"/>
@@ -5151,7 +5175,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>81</v>
@@ -5169,13 +5193,13 @@
         <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5204,16 +5228,16 @@
         <v>148</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
@@ -5244,13 +5268,13 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5258,13 +5282,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>79</v>
@@ -5289,13 +5313,13 @@
         <v>235</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5306,7 +5330,7 @@
         <v>79</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>79</v>
@@ -5324,10 +5348,10 @@
         <v>148</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
@@ -5366,38 +5390,40 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
@@ -5409,13 +5435,13 @@
         <v>235</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5426,7 +5452,7 @@
         <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>79</v>
@@ -5441,13 +5467,13 @@
         <v>79</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>79</v>
@@ -5465,13 +5491,13 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>79</v>
@@ -5486,58 +5512,58 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>235</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5561,13 +5587,13 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5585,7 +5611,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5603,59 +5629,61 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>106</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>107</v>
+        <v>286</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
       </c>
@@ -5679,13 +5707,13 @@
         <v>79</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5703,7 +5731,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>108</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5715,44 +5743,44 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>79</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>79</v>
+        <v>292</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>79</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>79</v>
@@ -5764,17 +5792,15 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5811,31 +5837,31 @@
         <v>79</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>79</v>
@@ -5858,14 +5884,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5881,23 +5907,21 @@
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5933,9 +5957,11 @@
         <v>79</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5943,7 +5969,7 @@
         <v>117</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>118</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5955,7 +5981,7 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
@@ -5967,7 +5993,7 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5976,16 +6002,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>79</v>
       </c>
@@ -5994,10 +6018,10 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -6009,16 +6033,16 @@
         <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6055,19 +6079,17 @@
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6091,7 +6113,7 @@
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>79</v>
@@ -6100,14 +6122,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6119,25 +6143,29 @@
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6185,19 +6213,19 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
@@ -6209,7 +6237,7 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
@@ -6220,21 +6248,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6246,17 +6274,15 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6293,31 +6319,31 @@
         <v>79</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
@@ -6338,48 +6364,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>309</v>
+        <v>112</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>310</v>
+        <v>113</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6388,7 +6412,7 @@
         <v>79</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>313</v>
+        <v>79</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>79</v>
@@ -6415,31 +6439,31 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>314</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
@@ -6451,7 +6475,7 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6462,10 +6486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6488,18 +6512,20 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6508,7 +6534,7 @@
         <v>79</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>79</v>
@@ -6547,7 +6573,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6562,7 +6588,7 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
@@ -6571,7 +6597,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6582,10 +6608,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6608,18 +6634,18 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>327</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6667,7 +6693,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6691,21 +6717,21 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
+      <c r="B41" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6713,13 +6739,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>
@@ -6728,17 +6754,17 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -6787,7 +6813,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6802,7 +6828,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>79</v>
@@ -6811,7 +6837,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6822,10 +6848,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6848,19 +6874,17 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6909,7 +6933,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6933,7 +6957,7 @@
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6942,12 +6966,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6955,13 +6979,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
@@ -6970,19 +6994,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7031,7 +7055,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7046,7 +7070,7 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>79</v>
@@ -7055,7 +7079,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7066,10 +7090,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7077,7 +7101,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7092,18 +7116,20 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7127,37 +7153,37 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
@@ -7166,30 +7192,30 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7203,24 +7229,26 @@
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>106</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7245,13 +7273,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7269,19 +7297,19 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>108</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7290,7 +7318,7 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>79</v>
@@ -7299,26 +7327,26 @@
         <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>79</v>
@@ -7330,17 +7358,15 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7377,31 +7403,31 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7424,14 +7450,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7447,23 +7473,21 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>113</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7499,9 +7523,11 @@
         <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7509,7 +7535,7 @@
         <v>117</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>297</v>
+        <v>118</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7521,7 +7547,7 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7533,7 +7559,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>298</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7542,16 +7568,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7560,10 +7584,10 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
@@ -7575,16 +7599,16 @@
         <v>144</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>366</v>
+        <v>298</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7609,29 +7633,29 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7655,7 +7679,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7664,14 +7688,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="B49" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7683,25 +7709,29 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>106</v>
+        <v>372</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7725,13 +7755,11 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7749,19 +7777,19 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7773,7 +7801,7 @@
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>304</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7784,21 +7812,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7810,17 +7838,15 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7857,31 +7883,31 @@
         <v>79</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7902,48 +7928,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>309</v>
+        <v>112</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>310</v>
+        <v>113</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7952,7 +7976,7 @@
         <v>79</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>79</v>
@@ -7979,31 +8003,31 @@
         <v>79</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>118</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8015,7 +8039,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8024,12 +8048,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8037,13 +8061,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>79</v>
@@ -8052,18 +8076,20 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8072,7 +8098,7 @@
         <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>79</v>
@@ -8111,7 +8137,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8135,7 +8161,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8144,12 +8170,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8157,13 +8183,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>79</v>
@@ -8172,18 +8198,18 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>327</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8231,7 +8257,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8246,7 +8272,7 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>79</v>
@@ -8255,7 +8281,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8264,12 +8290,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8277,13 +8303,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
@@ -8292,17 +8318,17 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8351,7 +8377,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8366,7 +8392,7 @@
         <v>103</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>79</v>
@@ -8375,7 +8401,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8386,10 +8412,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8412,19 +8438,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8473,7 +8497,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8497,7 +8521,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8508,10 +8532,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8534,19 +8558,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>386</v>
+        <v>347</v>
       </c>
       <c r="N56" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O56" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8595,7 +8619,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8619,7 +8643,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8628,26 +8652,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
@@ -8656,17 +8680,19 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>389</v>
+        <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>392</v>
+        <v>356</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8715,10 +8741,10 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -8733,16 +8759,16 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8750,18 +8776,18 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>91</v>
@@ -8776,18 +8802,18 @@
         <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8835,10 +8861,10 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>91</v>
@@ -8853,27 +8879,27 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>404</v>
-      </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8887,7 +8913,7 @@
         <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>79</v>
@@ -8896,16 +8922,16 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8955,7 +8981,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8973,16 +8999,16 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
@@ -8990,10 +9016,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9013,19 +9039,19 @@
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9075,7 +9101,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9084,7 +9110,7 @@
         <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>416</v>
+        <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
@@ -9093,13 +9119,13 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>417</v>
@@ -9108,7 +9134,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>418</v>
       </c>
@@ -9127,16 +9153,16 @@
         <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>212</v>
+        <v>411</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>419</v>
@@ -9144,7 +9170,9 @@
       <c r="M61" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N61" s="2"/>
+      <c r="N61" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9202,7 +9230,7 @@
         <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>103</v>
@@ -9217,21 +9245,21 @@
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>421</v>
+        <v>79</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9245,7 +9273,7 @@
         <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
@@ -9254,7 +9282,7 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>424</v>
+        <v>212</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>425</v>
@@ -9311,7 +9339,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9335,10 +9363,10 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>79</v>
@@ -9346,10 +9374,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9372,13 +9400,13 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9429,7 +9457,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9453,10 +9481,10 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>431</v>
+        <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>79</v>
@@ -9464,10 +9492,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9478,7 +9506,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9487,10 +9515,10 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>435</v>
@@ -9547,34 +9575,34 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="AO64" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>79</v>
@@ -9582,10 +9610,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9596,7 +9624,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -9608,13 +9636,13 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>105</v>
+        <v>440</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>106</v>
+        <v>441</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9665,19 +9693,19 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>108</v>
+        <v>439</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -9700,21 +9728,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>79</v>
@@ -9726,17 +9754,15 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9785,19 +9811,19 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>79</v>
@@ -9820,14 +9846,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>441</v>
+        <v>110</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9840,26 +9866,24 @@
         <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>442</v>
+        <v>112</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>443</v>
+        <v>113</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O67" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -9907,7 +9931,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9942,42 +9966,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10001,13 +10029,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>448</v>
+        <v>79</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>449</v>
+        <v>79</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10025,19 +10053,19 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>450</v>
+        <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
@@ -10046,10 +10074,10 @@
         <v>79</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>244</v>
+        <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10060,10 +10088,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10074,7 +10102,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10086,13 +10114,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10119,13 +10147,13 @@
         <v>79</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>79</v>
+        <v>454</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>79</v>
+        <v>455</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -10143,16 +10171,16 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>103</v>
@@ -10164,10 +10192,10 @@
         <v>79</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10178,10 +10206,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10192,7 +10220,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10204,13 +10232,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>235</v>
+        <v>459</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10237,13 +10265,13 @@
         <v>79</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>79</v>
@@ -10261,16 +10289,16 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>103</v>
@@ -10296,10 +10324,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10310,7 +10338,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>79</v>
@@ -10322,17 +10350,15 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>434</v>
+        <v>235</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N71" t="s" s="2">
         <v>464</v>
       </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10357,13 +10383,13 @@
         <v>79</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>79</v>
+        <v>466</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10381,19 +10407,19 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>465</v>
+        <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10416,10 +10442,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10430,7 +10456,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>79</v>
@@ -10442,15 +10468,17 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>105</v>
+        <v>440</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>106</v>
+        <v>468</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10499,19 +10527,19 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>108</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>79</v>
+        <v>471</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
@@ -10534,21 +10562,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>79</v>
@@ -10560,17 +10588,15 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10619,19 +10645,19 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
@@ -10654,14 +10680,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>441</v>
+        <v>110</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10674,26 +10700,24 @@
         <v>79</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>442</v>
+        <v>112</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>443</v>
+        <v>113</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O74" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
       </c>
@@ -10741,7 +10765,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>444</v>
+        <v>118</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10776,14 +10800,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10796,22 +10820,26 @@
         <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10835,13 +10863,13 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10859,7 +10887,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10868,25 +10896,25 @@
         <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>475</v>
+        <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>476</v>
+        <v>79</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
@@ -10894,10 +10922,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10920,13 +10948,13 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>478</v>
+        <v>235</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10953,13 +10981,13 @@
         <v>79</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>79</v>
@@ -10977,7 +11005,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10986,7 +11014,7 @@
         <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>103</v>
@@ -10995,27 +11023,27 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>79</v>
+        <v>481</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11029,22 +11057,22 @@
         <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J77" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K77" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11095,7 +11123,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11104,7 +11132,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>79</v>
+        <v>480</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>103</v>
@@ -11113,23 +11141,141 @@
         <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>485</v>
+        <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>486</v>
+        <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>79</v>
+        <v>482</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP77">
+  <autoFilter ref="A1:AP78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11139,7 +11285,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-fruehere-tumorerkrankung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
